--- a/JsonConverter/ExcelFiles/GachaProbabilityData.xlsx
+++ b/JsonConverter/ExcelFiles/GachaProbabilityData.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>고유 id</t>
   </si>
@@ -58,6 +58,9 @@
     <t>Companion_3</t>
   </si>
   <si>
+    <t>Companion_4</t>
+  </si>
+  <si>
     <t>Equipment_1</t>
   </si>
   <si>
@@ -65,6 +68,9 @@
   </si>
   <si>
     <t>Equipment_3</t>
+  </si>
+  <si>
+    <t>Equipment_4</t>
   </si>
 </sst>
 </file>
@@ -388,7 +394,7 @@
         <v>1.0</v>
       </c>
       <c r="D4" s="1">
-        <v>70.0</v>
+        <v>40.0</v>
       </c>
       <c r="E4" s="1">
         <v>10.0</v>
@@ -405,7 +411,7 @@
         <v>2.0</v>
       </c>
       <c r="D5" s="1">
-        <v>25.0</v>
+        <v>30.0</v>
       </c>
       <c r="E5" s="1">
         <v>30.0</v>
@@ -422,7 +428,7 @@
         <v>3.0</v>
       </c>
       <c r="D6" s="1">
-        <v>5.0</v>
+        <v>20.0</v>
       </c>
       <c r="E6" s="1">
         <v>100.0</v>
@@ -433,16 +439,16 @@
         <v>15</v>
       </c>
       <c r="B7" s="1">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="C7" s="1">
-        <v>1.0</v>
+        <v>4.0</v>
       </c>
       <c r="D7" s="1">
-        <v>70.0</v>
+        <v>10.0</v>
       </c>
       <c r="E7" s="1">
-        <v>10.0</v>
+        <v>200.0</v>
       </c>
     </row>
     <row r="8">
@@ -453,13 +459,13 @@
         <v>1.0</v>
       </c>
       <c r="C8" s="1">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="D8" s="1">
-        <v>25.0</v>
+        <v>40.0</v>
       </c>
       <c r="E8" s="1">
-        <v>30.0</v>
+        <v>10.0</v>
       </c>
     </row>
     <row r="9">
@@ -470,13 +476,47 @@
         <v>1.0</v>
       </c>
       <c r="C9" s="1">
+        <v>2.0</v>
+      </c>
+      <c r="D9" s="1">
+        <v>30.0</v>
+      </c>
+      <c r="E9" s="1">
+        <v>30.0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C10" s="1">
         <v>3.0</v>
       </c>
-      <c r="D9" s="1">
-        <v>5.0</v>
-      </c>
-      <c r="E9" s="1">
+      <c r="D10" s="1">
+        <v>20.0</v>
+      </c>
+      <c r="E10" s="1">
         <v>100.0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1.0</v>
+      </c>
+      <c r="C11" s="1">
+        <v>4.0</v>
+      </c>
+      <c r="D11" s="1">
+        <v>10.0</v>
+      </c>
+      <c r="E11" s="1">
+        <v>200.0</v>
       </c>
     </row>
   </sheetData>
